--- a/.claude/context/asof-delivery-tracker.xlsx
+++ b/.claude/context/asof-delivery-tracker.xlsx
@@ -2070,7 +2070,7 @@
       </c>
       <c r="F19" s="43" t="inlineStr">
         <is>
-          <t>CLI pipeline verified against fixtures; still needs real Jira/GitHub credentials + lead review to clear the GO/NO-GO gate</t>
+          <t>Real Jira Cloud site + real GitHub repo connected; sync/drift/brief run live end to end. D1 (KAN-16 Done w/ unmerged PR) and D2 (KAN-15/18/37 stale In Progress, 2 of them moved by a real second team member, Alex Cooper) both verified firing correctly. Still needs: your own usefulness judgment on the findings to actually clear the GO/NO-GO gate.</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="I18" s="43" t="inlineStr">
         <is>
-          <t>src/cli/{sync,drift,brief}.ts built and verified end-to-end against real local Postgres, incl. auto-resolve (test/fixtures/demoTeam.ts, ASOF_DEMO_PHASE=1/2). NOT done: the actual GO/NO-GO gate needs a real team's Jira+GitHub data and a lead's usefulness judgment -- neither is something this session can perform. Next: point .env at a real Jira project + GitHub repo and run the 3 commands for real.</t>
+          <t>First real sync+drift+brief run completed against a real Jira Cloud site (KAN project) + real GitHub repo (vinaycookscode/AsOf), with a second real team member (Alex Cooper) independently active on the board. Fixed 3 real bugs the live run surfaced: Jira's /rest/api/3/search was removed (migrated to /rest/api/3/search/jql, cursor pagination); fetchActiveSprint crashed on Kanban boards (400 'board does not support sprints') instead of treating it as sprint=null; brief prompt leaked a literal 'Sprint day X of Y' placeholder when sprint was null. D1 and D2 both verified firing correctly on real data (issues transitioned via the Jira API directly, since CSV-imported issues have no changelog history for their seeded status). STILL NOT DONE: the actual GO/NO-GO judgment call -- are these findings useful -- is the user's to make, not something this session can perform.</t>
         </is>
       </c>
     </row>

--- a/.claude/context/asof-delivery-tracker.xlsx
+++ b/.claude/context/asof-delivery-tracker.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="D22" s="43" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E22" s="43" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="F22" s="43" t="inlineStr">
         <is>
-          <t>Highest technical risk - do early</t>
+          <t>Explicit (B7) + branch/commit-ref (B8) + fuzzy via Haiku (B19), all fixture-tested.</t>
         </is>
       </c>
     </row>
@@ -3706,10 +3706,14 @@
       </c>
       <c r="H23" s="43" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I23" s="43" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I23" s="43" t="inlineStr">
+        <is>
+          <t>src/linking/fuzzy.ts -- extractFuzzyLinks() only calls Haiku for PRs no rule-based source matched, offers the connected project's issue titles as candidates, discards &lt;0.5 confidence and any hallucinated key not in the offered list. linkSource always 'fuzzy' -- D1/D2/D6 already exclude fuzzy from their linking gate (drift-rules-spec.md), so this can only ever support Medium/Low findings, never drive a High one. Wired into resolveLinksWithFuzzy()/cli/sync.ts as opt-in: only runs when ANTHROPIC_API_KEY is set, otherwise npm run sync stays on the existing synchronous rule-based-only path. 9 fixture tests (TP/boundary/FP-trap/resolution + prompt-parsing edge cases) against a mocked FuzzyLinkerClient, no live API calls in CI.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="24">
       <c r="A24" s="41" t="inlineStr">

--- a/.claude/context/asof-delivery-tracker.xlsx
+++ b/.claude/context/asof-delivery-tracker.xlsx
@@ -2180,7 +2180,7 @@
       </c>
       <c r="D23" s="43" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E23" s="43" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F23" s="43" t="inlineStr">
         <is>
-          <t>All 8 rules (D1-D8) implemented and fixture-tested (B10-B12, B20-B24). Per-team rule config API (B26) not started.</t>
+          <t>All 8 rules (B10-B12, B20-B24) + per-team rule config API (B26), all verified live against real Jira data.</t>
         </is>
       </c>
     </row>
@@ -4035,10 +4035,14 @@
       </c>
       <c r="H30" s="43" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I30" s="43" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I30" s="43" t="inlineStr">
+        <is>
+          <t>src/db/ruleConfig.ts + src/api/routes/settings.ts. GET/PUT /api/settings/rules/:ruleId reads/writes the existing (previously unused) rule_config table -- enabled/params/slackDelivery merged onto drift-rules-spec.md defaults. cli/drift.ts now loads per-team config instead of hardcoded DEFAULT_RULE_CONFIG and filters disabled rules' findings before persisting (which auto-resolves their previously-open findings for free via B25's lifecycle). Also added team.status_category_map (migration 003) + GET/PUT /api/settings/status-map for the onboarding workflow-mapping step (design-spec.md 2.1); cli/sync.ts loads it before constructing JiraClient. No onboarding UI writes to it yet (B15/B34). Verified live against the real KAN team: disabled D2 via the API, findings correctly auto-resolved (not deleted); raised d2.days to 10, confirmed suppression; reset to defaults, findings reopened in place without duplicating.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="23.25" customHeight="1" s="24">
       <c r="A31" s="41" t="inlineStr">

--- a/.claude/context/asof-delivery-tracker.xlsx
+++ b/.claude/context/asof-delivery-tracker.xlsx
@@ -2222,7 +2222,7 @@
       </c>
       <c r="F24" s="43" t="inlineStr">
         <is>
-          <t>src/llm/ask.ts + src/llm/queryTools.ts + POST /api/ask + apps/web Jarvis screen (voice + text). SSE streaming not implemented (single-shot request/response instead); source chips inline not implemented for the voice answer text (spoken answers avoid markdown by design)</t>
+          <t>src/llm/ask.ts + src/llm/queryTools.ts + POST /api/ask + apps/web Jarvis screen (voice+text) + apps/web Ask screen (B33, text chat with real clickable source chips, suggested prompts). SSE streaming still not implemented in either (single-shot request/response); voice answers still skip chips by design (spoken text avoids markdown).</t>
         </is>
       </c>
     </row>
@@ -4356,10 +4356,14 @@
       </c>
       <c r="H37" s="43" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I37" s="43" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I37" s="43" t="inlineStr">
+        <is>
+          <t>apps/web/src/pages/Ask.tsx -- text chat over the existing /api/ask backend (B28), Send button + Enter-to-submit, 3 suggested prompts in empty state per design-spec.md 2.4, multi-turn history. Source chips are real: extended AskResult with sources (entity -&gt; sourceUrl) via collectSources() in src/llm/ask.ts, walking tool results for Finding-shaped (entityRefs+evidence) and label+sourceUrl-shaped data -- same evidence-matching pattern FindingCard.tsx already uses. NOT done: SSE token streaming (same documented gap as Jarvis) -- would need reworking the tool-use loop for both providers, deferred rather than partial. Verified live against the real KAN team: correct honest 'no team member found' response when the local model picked the wrong tool; a drift-findings question returned all 4 real findings with KAN-16/PR #2/KAN-15 etc rendered as clickable chips to the real Jira/GitHub URLs.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="23.25" customHeight="1" s="24">
       <c r="A38" s="41" t="inlineStr">
